--- a/research/traditional_assets/database/data/malawi/malawi_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malawi/malawi_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2275</v>
+        <v>0.265</v>
       </c>
       <c r="E2">
-        <v>0.15</v>
+        <v>0.163</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>7.279129947870668e-06</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>4.691911165340392e-06</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>104.8</v>
+        <v>130.12</v>
       </c>
       <c r="L2">
-        <v>0.2330960854092527</v>
+        <v>0.256192163811774</v>
       </c>
       <c r="M2">
-        <v>34.0866</v>
+        <v>61.83</v>
       </c>
       <c r="N2">
-        <v>0.02580168041783362</v>
+        <v>0.03767594905855828</v>
       </c>
       <c r="O2">
-        <v>0.3252538167938931</v>
+        <v>0.4751767599139256</v>
       </c>
       <c r="P2">
-        <v>34.0866</v>
+        <v>61.83</v>
       </c>
       <c r="Q2">
-        <v>0.02580168041783362</v>
+        <v>0.03767594905855828</v>
       </c>
       <c r="R2">
-        <v>0.3252538167938931</v>
+        <v>0.4751767599139256</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>394.2</v>
+        <v>616</v>
       </c>
       <c r="V2">
-        <v>0.2983877072136856</v>
+        <v>0.3753579915910061</v>
       </c>
       <c r="W2">
-        <v>0.2207446808510638</v>
+        <v>0.3537074148296593</v>
       </c>
       <c r="X2">
-        <v>0.09986391991639335</v>
+        <v>0.1979642094907424</v>
       </c>
       <c r="Y2">
-        <v>0.1208807609346705</v>
+        <v>0.1557432053389169</v>
       </c>
       <c r="Z2">
-        <v>1.343518749320872</v>
+        <v>1.195115064238317</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09649285586104371</v>
+        <v>0.1800071766378755</v>
       </c>
       <c r="AC2">
-        <v>-0.09649285586104371</v>
+        <v>-0.1800071766378755</v>
       </c>
       <c r="AD2">
-        <v>470.5</v>
+        <v>437.409</v>
       </c>
       <c r="AE2">
-        <v>0.003636515877186739</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>470.5036365158772</v>
+        <v>437.409</v>
       </c>
       <c r="AG2">
-        <v>76.3036365158772</v>
+        <v>-178.591</v>
       </c>
       <c r="AH2">
-        <v>0.2626159195740769</v>
+        <v>0.2104436401285729</v>
       </c>
       <c r="AI2">
-        <v>0.476168307784906</v>
+        <v>0.4459675635113463</v>
       </c>
       <c r="AJ2">
-        <v>0.05460386285105409</v>
+        <v>-0.1221127528104101</v>
       </c>
       <c r="AK2">
-        <v>0.1284781432952841</v>
+        <v>-0.4895465846511463</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>117625</v>
-      </c>
-      <c r="AP2">
-        <v>19075.9091289693</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.113</v>
+        <v>0.133</v>
       </c>
       <c r="E3">
-        <v>0.0689</v>
+        <v>0.101</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +722,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>3.448574103859486e-05</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.258856231199337e-05</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
       <c r="L3">
-        <v>0.2961011591148577</v>
+        <v>0.2849949647532729</v>
       </c>
       <c r="M3">
-        <v>10.7</v>
+        <v>15.8</v>
       </c>
       <c r="N3">
-        <v>0.02659706686552324</v>
+        <v>0.034550623223267</v>
       </c>
       <c r="O3">
-        <v>0.3807829181494661</v>
+        <v>0.558303886925795</v>
       </c>
       <c r="P3">
-        <v>10.7</v>
+        <v>15.8</v>
       </c>
       <c r="Q3">
-        <v>0.02659706686552324</v>
+        <v>0.034550623223267</v>
       </c>
       <c r="R3">
-        <v>0.3807829181494661</v>
+        <v>0.558303886925795</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +758,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>35.4</v>
+        <v>37.8</v>
       </c>
       <c r="V3">
-        <v>0.08799403430275912</v>
+        <v>0.08265908593920838</v>
       </c>
       <c r="W3">
-        <v>0.207380073800738</v>
+        <v>0.2090103397341211</v>
       </c>
       <c r="X3">
-        <v>0.09135997388047509</v>
+        <v>0.1568859011345416</v>
       </c>
       <c r="Y3">
-        <v>0.1160200999202629</v>
+        <v>0.05212443859957946</v>
       </c>
       <c r="Z3">
-        <v>0.9451848886468681</v>
+        <v>0.993</v>
       </c>
       <c r="AA3">
-        <v>2.135036775355429e-05</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.09135978051133169</v>
+        <v>0.1568717230701905</v>
       </c>
       <c r="AC3">
-        <v>-0.09133843014357813</v>
+        <v>-0.1568717230701905</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="AE3">
-        <v>0.003636515877186739</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.003636515877186739</v>
+        <v>0.309</v>
       </c>
       <c r="AG3">
-        <v>-35.39636348412281</v>
+        <v>-37.491</v>
       </c>
       <c r="AH3">
-        <v>9.039231931087009e-06</v>
+        <v>0.0006752489570790784</v>
       </c>
       <c r="AI3">
-        <v>2.685685533091519e-05</v>
+        <v>0.002503869247785818</v>
       </c>
       <c r="AJ3">
-        <v>-0.09647318794724206</v>
+        <v>-0.08930489817988656</v>
       </c>
       <c r="AK3">
-        <v>-0.3539507633655208</v>
+        <v>-0.437932927612751</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>-8849.090871030701</v>
       </c>
     </row>
     <row r="4">
@@ -844,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="E4">
-        <v>0.15</v>
+        <v>0.163</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>33.2</v>
+        <v>42.8</v>
       </c>
       <c r="L4">
-        <v>0.2966934763181412</v>
+        <v>0.314013206162876</v>
       </c>
       <c r="M4">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="N4">
-        <v>0.02483801295896328</v>
+        <v>0.02700781805259417</v>
       </c>
       <c r="O4">
-        <v>0.3463855421686747</v>
+        <v>0.4439252336448599</v>
       </c>
       <c r="P4">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="Q4">
-        <v>0.02483801295896328</v>
+        <v>0.02700781805259417</v>
       </c>
       <c r="R4">
-        <v>0.3463855421686747</v>
+        <v>0.4439252336448599</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>50.9</v>
+        <v>187.4</v>
       </c>
       <c r="V4">
-        <v>0.1099352051835853</v>
+        <v>0.2663823738450604</v>
       </c>
       <c r="W4">
-        <v>0.2207446808510638</v>
+        <v>0.2808398950131233</v>
       </c>
       <c r="X4">
-        <v>0.09444940075886868</v>
+        <v>0.1669184152773407</v>
       </c>
       <c r="Y4">
-        <v>0.1262952800921952</v>
+        <v>0.1139214797357826</v>
       </c>
       <c r="Z4">
-        <v>0.8354487083768852</v>
+        <v>2.326732673267327</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09340342079785395</v>
+        <v>0.163541904370982</v>
       </c>
       <c r="AC4">
-        <v>-0.09340342079785395</v>
+        <v>-0.163541904370982</v>
       </c>
       <c r="AD4">
-        <v>26.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>26.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="AG4">
-        <v>-24.1</v>
+        <v>-101.5</v>
       </c>
       <c r="AH4">
-        <v>0.05471621069824418</v>
+        <v>0.108816822903471</v>
       </c>
       <c r="AI4">
-        <v>0.1396560708702449</v>
+        <v>0.3242733106832767</v>
       </c>
       <c r="AJ4">
-        <v>-0.05491000227842333</v>
+        <v>-0.1686046511627907</v>
       </c>
       <c r="AK4">
-        <v>-0.1709219858156028</v>
+        <v>-1.309677419354839</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NBS Bank Plc (MAL:NBS)</t>
+          <t>FDH Bank Plc (MAL:FDHB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -965,6 +953,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.403</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -978,28 +969,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>10.6</v>
+        <v>14.3</v>
       </c>
       <c r="L5">
-        <v>0.2236286919831224</v>
+        <v>0.2667910447761194</v>
       </c>
       <c r="M5">
-        <v>2.88</v>
+        <v>10.2</v>
       </c>
       <c r="N5">
-        <v>0.03529411764705882</v>
+        <v>0.08710503842869342</v>
       </c>
       <c r="O5">
-        <v>0.2716981132075472</v>
+        <v>0.7132867132867132</v>
       </c>
       <c r="P5">
-        <v>2.88</v>
+        <v>10.2</v>
       </c>
       <c r="Q5">
-        <v>0.03529411764705882</v>
+        <v>0.08710503842869342</v>
       </c>
       <c r="R5">
-        <v>0.2716981132075472</v>
+        <v>0.7132867132867132</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +999,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>20.6</v>
+        <v>85.5</v>
       </c>
       <c r="V5">
-        <v>0.2524509803921569</v>
+        <v>0.7301451750640479</v>
       </c>
       <c r="W5">
-        <v>0.5096153846153846</v>
+        <v>0.4097421203438396</v>
       </c>
       <c r="X5">
-        <v>0.09986391991639335</v>
+        <v>0.1979642094907424</v>
       </c>
       <c r="Y5">
-        <v>0.4097514646989913</v>
+        <v>0.2117779108530972</v>
       </c>
       <c r="Z5">
-        <v>2.164383561643835</v>
+        <v>5.890109890109885</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09649285586104371</v>
+        <v>0.1800071766378755</v>
       </c>
       <c r="AC5">
-        <v>-0.09649285586104371</v>
+        <v>-0.1800071766378755</v>
       </c>
       <c r="AD5">
-        <v>13</v>
+        <v>58.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>58.3</v>
       </c>
       <c r="AG5">
-        <v>-7.600000000000001</v>
+        <v>-27.2</v>
       </c>
       <c r="AH5">
-        <v>0.1374207188160677</v>
+        <v>0.3323831242873432</v>
       </c>
       <c r="AI5">
-        <v>0.3087885985748218</v>
+        <v>0.6016511867905057</v>
       </c>
       <c r="AJ5">
-        <v>-0.1027027027027027</v>
+        <v>-0.3025583982202448</v>
       </c>
       <c r="AK5">
-        <v>-0.3534883720930233</v>
+        <v>-2.385964912280703</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FDH Bank Plc (MAL:FDHB)</t>
+          <t>FMBcapital Holdings Plc (MAL:FMBCH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,7 +1073,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.382</v>
+        <v>0.36</v>
+      </c>
+      <c r="E6">
+        <v>0.341</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,28 +1091,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>35.3</v>
       </c>
       <c r="L6">
-        <v>0.3350970017636684</v>
+        <v>0.2061915887850467</v>
       </c>
       <c r="M6">
-        <v>4.09</v>
+        <v>12.2</v>
       </c>
       <c r="N6">
-        <v>0.03063670411985019</v>
+        <v>0.04577861163227016</v>
       </c>
       <c r="O6">
-        <v>0.2152631578947368</v>
+        <v>0.3456090651558074</v>
       </c>
       <c r="P6">
-        <v>4.09</v>
+        <v>12.2</v>
       </c>
       <c r="Q6">
-        <v>0.03063670411985019</v>
+        <v>0.04577861163227016</v>
       </c>
       <c r="R6">
-        <v>0.2152631578947368</v>
+        <v>0.3456090651558074</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1127,55 +1121,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>22.6</v>
+        <v>290.4</v>
       </c>
       <c r="V6">
-        <v>0.1692883895131086</v>
+        <v>1.08968105065666</v>
       </c>
       <c r="W6">
-        <v>0.6050955414012739</v>
+        <v>0.3537074148296593</v>
       </c>
       <c r="X6">
-        <v>0.1175104989415703</v>
+        <v>0.2064027045946401</v>
       </c>
       <c r="Y6">
-        <v>0.4875850424597035</v>
+        <v>0.1473047102350191</v>
       </c>
       <c r="Z6">
-        <v>1.343601895734597</v>
+        <v>0.8542914171656685</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1036421633158578</v>
+        <v>0.1829788549358703</v>
       </c>
       <c r="AC6">
-        <v>-0.1036421633158578</v>
+        <v>-0.1829788549358703</v>
       </c>
       <c r="AD6">
-        <v>65.40000000000001</v>
+        <v>159.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>65.40000000000001</v>
+        <v>159.9</v>
       </c>
       <c r="AG6">
-        <v>42.8</v>
+        <v>-130.5</v>
       </c>
       <c r="AH6">
-        <v>0.3288084464555053</v>
+        <v>0.3750000000000001</v>
       </c>
       <c r="AI6">
-        <v>0.6494538232373387</v>
+        <v>0.4783128926114268</v>
       </c>
       <c r="AJ6">
-        <v>0.2427680090754396</v>
+        <v>-0.9595588235294114</v>
       </c>
       <c r="AK6">
-        <v>0.5480153649167735</v>
+        <v>-2.972665148063778</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1186,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FMBcapital Holdings Plc (MAL:FMBCH)</t>
+          <t>NBS Bank Plc (MAL:NBS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,10 +1195,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.319</v>
-      </c>
-      <c r="E7">
-        <v>0.301</v>
+        <v>0.265</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,28 +1210,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>13.9</v>
+        <v>9.42</v>
       </c>
       <c r="L7">
-        <v>0.1002162941600577</v>
+        <v>0.1983157894736842</v>
       </c>
       <c r="M7">
-        <v>4.916600000000001</v>
+        <v>4.63</v>
       </c>
       <c r="N7">
-        <v>0.02042625675114251</v>
+        <v>0.04788004136504653</v>
       </c>
       <c r="O7">
-        <v>0.3537122302158274</v>
+        <v>0.4915074309978769</v>
       </c>
       <c r="P7">
-        <v>4.916600000000001</v>
+        <v>4.63</v>
       </c>
       <c r="Q7">
-        <v>0.02042625675114251</v>
+        <v>0.04788004136504653</v>
       </c>
       <c r="R7">
-        <v>0.3537122302158274</v>
+        <v>0.4915074309978769</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1249,55 +1240,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>264.7</v>
+        <v>14.9</v>
       </c>
       <c r="V7">
-        <v>1.099709181553801</v>
+        <v>0.1540847983453981</v>
       </c>
       <c r="W7">
-        <v>0.1816993464052288</v>
+        <v>0.3798387096774193</v>
       </c>
       <c r="X7">
-        <v>0.1723745080996698</v>
+        <v>0.2704660597758619</v>
       </c>
       <c r="Y7">
-        <v>0.009324838305558941</v>
+        <v>0.1093726499015574</v>
       </c>
       <c r="Z7">
-        <v>3.831491712707177</v>
+        <v>0.8347978910369069</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1138773420945137</v>
+        <v>0.1972049151608007</v>
       </c>
       <c r="AC7">
-        <v>-0.1138773420945137</v>
+        <v>-0.1972049151608007</v>
       </c>
       <c r="AD7">
-        <v>365.3</v>
+        <v>133</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>365.3</v>
+        <v>133</v>
       </c>
       <c r="AG7">
-        <v>100.6</v>
+        <v>118.1</v>
       </c>
       <c r="AH7">
-        <v>0.6028052805280528</v>
+        <v>0.5790161079669134</v>
       </c>
       <c r="AI7">
-        <v>0.7052123552123553</v>
+        <v>0.8245505269683818</v>
       </c>
       <c r="AJ7">
-        <v>0.2947553472018752</v>
+        <v>0.5498137802607076</v>
       </c>
       <c r="AK7">
-        <v>0.3971575207264114</v>
+        <v>0.8066939890710382</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/research/traditional_assets/database/data/malawi/malawi_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malawi/malawi_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.265</v>
+        <v>0.339</v>
       </c>
       <c r="E2">
-        <v>0.163</v>
+        <v>0.7895000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>130.12</v>
+        <v>101.1</v>
       </c>
       <c r="L2">
-        <v>0.256192163811774</v>
+        <v>0.340518693162681</v>
       </c>
       <c r="M2">
-        <v>61.83</v>
+        <v>29.69</v>
       </c>
       <c r="N2">
-        <v>0.03767594905855828</v>
+        <v>0.02869985500241663</v>
       </c>
       <c r="O2">
-        <v>0.4751767599139256</v>
+        <v>0.2936696340257171</v>
       </c>
       <c r="P2">
-        <v>61.83</v>
+        <v>29.69</v>
       </c>
       <c r="Q2">
-        <v>0.03767594905855828</v>
+        <v>0.02869985500241663</v>
       </c>
       <c r="R2">
-        <v>0.4751767599139256</v>
+        <v>0.2936696340257171</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>616</v>
+        <v>121.3</v>
       </c>
       <c r="V2">
-        <v>0.3753579915910061</v>
+        <v>0.1172547124214596</v>
       </c>
       <c r="W2">
-        <v>0.3537074148296593</v>
+        <v>0.5995717344753747</v>
       </c>
       <c r="X2">
-        <v>0.1979642094907424</v>
+        <v>0.1292800699742405</v>
       </c>
       <c r="Y2">
-        <v>0.1557432053389169</v>
+        <v>0.4702916645011342</v>
       </c>
       <c r="Z2">
-        <v>1.195115064238317</v>
+        <v>1.020945018895564</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1800071766378755</v>
+        <v>0.1292647463217303</v>
       </c>
       <c r="AC2">
-        <v>-0.1800071766378755</v>
+        <v>-0.1292647463217303</v>
       </c>
       <c r="AD2">
-        <v>437.409</v>
+        <v>27.836</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>437.409</v>
+        <v>27.836</v>
       </c>
       <c r="AG2">
-        <v>-178.591</v>
+        <v>-93.464</v>
       </c>
       <c r="AH2">
-        <v>0.2104436401285729</v>
+        <v>0.02620263268871618</v>
       </c>
       <c r="AI2">
-        <v>0.4459675635113463</v>
+        <v>0.1004416604122164</v>
       </c>
       <c r="AJ2">
-        <v>-0.1221127528104101</v>
+        <v>-0.09932032355829107</v>
       </c>
       <c r="AK2">
-        <v>-0.4895465846511463</v>
+        <v>-0.5997587207063837</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.133</v>
+        <v>0.242</v>
       </c>
       <c r="E3">
-        <v>0.101</v>
+        <v>0.395</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>28.3</v>
+        <v>48.2</v>
       </c>
       <c r="L3">
-        <v>0.2849949647532729</v>
+        <v>0.3370629370629371</v>
       </c>
       <c r="M3">
-        <v>15.8</v>
+        <v>5.5</v>
       </c>
       <c r="N3">
-        <v>0.034550623223267</v>
+        <v>0.01001821493624772</v>
       </c>
       <c r="O3">
-        <v>0.558303886925795</v>
+        <v>0.1141078838174274</v>
       </c>
       <c r="P3">
-        <v>15.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q3">
-        <v>0.034550623223267</v>
+        <v>0.01001821493624772</v>
       </c>
       <c r="R3">
-        <v>0.558303886925795</v>
+        <v>0.1141078838174274</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>37.8</v>
+        <v>49.7</v>
       </c>
       <c r="V3">
-        <v>0.08265908593920838</v>
+        <v>0.09052823315118398</v>
       </c>
       <c r="W3">
-        <v>0.2090103397341211</v>
+        <v>0.3915515840779854</v>
       </c>
       <c r="X3">
-        <v>0.1568859011345416</v>
+        <v>0.1260179584888839</v>
       </c>
       <c r="Y3">
-        <v>0.05212443859957946</v>
+        <v>0.2655336255891015</v>
       </c>
       <c r="Z3">
-        <v>0.993</v>
+        <v>1.670385123059491</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1568717230701905</v>
+        <v>0.1260166804553518</v>
       </c>
       <c r="AC3">
-        <v>-0.1568717230701905</v>
+        <v>-0.1260166804553518</v>
       </c>
       <c r="AD3">
-        <v>0.309</v>
+        <v>0.236</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.309</v>
+        <v>0.236</v>
       </c>
       <c r="AG3">
-        <v>-37.491</v>
+        <v>-49.46400000000001</v>
       </c>
       <c r="AH3">
-        <v>0.0006752489570790784</v>
+        <v>0.0004296877844860861</v>
       </c>
       <c r="AI3">
-        <v>0.002503869247785818</v>
+        <v>0.001513441411861277</v>
       </c>
       <c r="AJ3">
-        <v>-0.08930489817988656</v>
+        <v>-0.09901989045834536</v>
       </c>
       <c r="AK3">
-        <v>-0.437932927612751</v>
+        <v>-0.4656048797017961</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Bank of Malawi plc (MAL:NBM)</t>
+          <t>NBS Bank Plc (MAL:NBS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.138</v>
+        <v>0.339</v>
       </c>
       <c r="E4">
-        <v>0.163</v>
+        <v>1.184</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>42.8</v>
+        <v>24.9</v>
       </c>
       <c r="L4">
-        <v>0.314013206162876</v>
+        <v>0.3246414602346805</v>
       </c>
       <c r="M4">
-        <v>19</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N4">
-        <v>0.02700781805259417</v>
+        <v>0.04425981873111782</v>
       </c>
       <c r="O4">
-        <v>0.4439252336448599</v>
+        <v>0.353012048192771</v>
       </c>
       <c r="P4">
-        <v>19</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Q4">
-        <v>0.02700781805259417</v>
+        <v>0.04425981873111782</v>
       </c>
       <c r="R4">
-        <v>0.4439252336448599</v>
+        <v>0.353012048192771</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>187.4</v>
+        <v>42.3</v>
       </c>
       <c r="V4">
-        <v>0.2663823738450604</v>
+        <v>0.2129909365558912</v>
       </c>
       <c r="W4">
-        <v>0.2808398950131233</v>
+        <v>0.8798586572438162</v>
       </c>
       <c r="X4">
-        <v>0.1669184152773407</v>
+        <v>0.1292800699742405</v>
       </c>
       <c r="Y4">
-        <v>0.1139214797357826</v>
+        <v>0.7505785872695756</v>
       </c>
       <c r="Z4">
-        <v>2.326732673267327</v>
+        <v>0.5239071038251366</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.163541904370982</v>
+        <v>0.1292647463217303</v>
       </c>
       <c r="AC4">
-        <v>-0.163541904370982</v>
+        <v>-0.1292647463217303</v>
       </c>
       <c r="AD4">
-        <v>85.90000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>85.90000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="AG4">
-        <v>-101.5</v>
+        <v>-31.6</v>
       </c>
       <c r="AH4">
-        <v>0.108816822903471</v>
+        <v>0.05112279025322504</v>
       </c>
       <c r="AI4">
-        <v>0.3242733106832767</v>
+        <v>0.1996268656716418</v>
       </c>
       <c r="AJ4">
-        <v>-0.1686046511627907</v>
+        <v>-0.1892215568862275</v>
       </c>
       <c r="AK4">
-        <v>-1.309677419354839</v>
+        <v>-2.79646017699115</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.403</v>
+        <v>0.405</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,28 +969,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>14.3</v>
+        <v>28</v>
       </c>
       <c r="L5">
-        <v>0.2667910447761194</v>
+        <v>0.3626943005181347</v>
       </c>
       <c r="M5">
-        <v>10.2</v>
+        <v>15.4</v>
       </c>
       <c r="N5">
-        <v>0.08710503842869342</v>
+        <v>0.05367723945625654</v>
       </c>
       <c r="O5">
-        <v>0.7132867132867132</v>
+        <v>0.55</v>
       </c>
       <c r="P5">
-        <v>10.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q5">
-        <v>0.08710503842869342</v>
+        <v>0.05367723945625654</v>
       </c>
       <c r="R5">
-        <v>0.7132867132867132</v>
+        <v>0.55</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -999,301 +999,60 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>85.5</v>
+        <v>29.3</v>
       </c>
       <c r="V5">
-        <v>0.7301451750640479</v>
+        <v>0.1021261763680725</v>
       </c>
       <c r="W5">
-        <v>0.4097421203438396</v>
+        <v>0.5995717344753747</v>
       </c>
       <c r="X5">
-        <v>0.1979642094907424</v>
+        <v>0.1295869744944754</v>
       </c>
       <c r="Y5">
-        <v>0.2117779108530972</v>
+        <v>0.4699847599808993</v>
       </c>
       <c r="Z5">
-        <v>5.890109890109885</v>
+        <v>1.312925170068027</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1800071766378755</v>
+        <v>0.1294492964237625</v>
       </c>
       <c r="AC5">
-        <v>-0.1800071766378755</v>
+        <v>-0.1294492964237625</v>
       </c>
       <c r="AD5">
-        <v>58.3</v>
+        <v>16.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>58.3</v>
+        <v>16.9</v>
       </c>
       <c r="AG5">
-        <v>-27.2</v>
+        <v>-12.4</v>
       </c>
       <c r="AH5">
-        <v>0.3323831242873432</v>
+        <v>0.05562870309414088</v>
       </c>
       <c r="AI5">
-        <v>0.6016511867905057</v>
+        <v>0.25</v>
       </c>
       <c r="AJ5">
-        <v>-0.3025583982202448</v>
+        <v>-0.04517304189435338</v>
       </c>
       <c r="AK5">
-        <v>-2.385964912280703</v>
+        <v>-0.3237597911227155</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FMBcapital Holdings Plc (MAL:FMBCH)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.36</v>
-      </c>
-      <c r="E6">
-        <v>0.341</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>35.3</v>
-      </c>
-      <c r="L6">
-        <v>0.2061915887850467</v>
-      </c>
-      <c r="M6">
-        <v>12.2</v>
-      </c>
-      <c r="N6">
-        <v>0.04577861163227016</v>
-      </c>
-      <c r="O6">
-        <v>0.3456090651558074</v>
-      </c>
-      <c r="P6">
-        <v>12.2</v>
-      </c>
-      <c r="Q6">
-        <v>0.04577861163227016</v>
-      </c>
-      <c r="R6">
-        <v>0.3456090651558074</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>290.4</v>
-      </c>
-      <c r="V6">
-        <v>1.08968105065666</v>
-      </c>
-      <c r="W6">
-        <v>0.3537074148296593</v>
-      </c>
-      <c r="X6">
-        <v>0.2064027045946401</v>
-      </c>
-      <c r="Y6">
-        <v>0.1473047102350191</v>
-      </c>
-      <c r="Z6">
-        <v>0.8542914171656685</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.1829788549358703</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1829788549358703</v>
-      </c>
-      <c r="AD6">
-        <v>159.9</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>159.9</v>
-      </c>
-      <c r="AG6">
-        <v>-130.5</v>
-      </c>
-      <c r="AH6">
-        <v>0.3750000000000001</v>
-      </c>
-      <c r="AI6">
-        <v>0.4783128926114268</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.9595588235294114</v>
-      </c>
-      <c r="AK6">
-        <v>-2.972665148063778</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NBS Bank Plc (MAL:NBS)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.265</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>9.42</v>
-      </c>
-      <c r="L7">
-        <v>0.1983157894736842</v>
-      </c>
-      <c r="M7">
-        <v>4.63</v>
-      </c>
-      <c r="N7">
-        <v>0.04788004136504653</v>
-      </c>
-      <c r="O7">
-        <v>0.4915074309978769</v>
-      </c>
-      <c r="P7">
-        <v>4.63</v>
-      </c>
-      <c r="Q7">
-        <v>0.04788004136504653</v>
-      </c>
-      <c r="R7">
-        <v>0.4915074309978769</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>14.9</v>
-      </c>
-      <c r="V7">
-        <v>0.1540847983453981</v>
-      </c>
-      <c r="W7">
-        <v>0.3798387096774193</v>
-      </c>
-      <c r="X7">
-        <v>0.2704660597758619</v>
-      </c>
-      <c r="Y7">
-        <v>0.1093726499015574</v>
-      </c>
-      <c r="Z7">
-        <v>0.8347978910369069</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.1972049151608007</v>
-      </c>
-      <c r="AC7">
-        <v>-0.1972049151608007</v>
-      </c>
-      <c r="AD7">
-        <v>133</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>133</v>
-      </c>
-      <c r="AG7">
-        <v>118.1</v>
-      </c>
-      <c r="AH7">
-        <v>0.5790161079669134</v>
-      </c>
-      <c r="AI7">
-        <v>0.8245505269683818</v>
-      </c>
-      <c r="AJ7">
-        <v>0.5498137802607076</v>
-      </c>
-      <c r="AK7">
-        <v>0.8066939890710382</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>
